--- a/docs/桃源农场_开发计划.xlsx
+++ b/docs/桃源农场_开发计划.xlsx
@@ -1413,37 +1413,37 @@
       <c r="G25" s="4" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>阶段二</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>阶段一</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>地图系统</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>地图编辑器（浏览器内嵌方案）</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>★★☆</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>★★☆</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>⏳ 待开始</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>vs Tiled工具，待方案确认</t>
         </is>
